--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260820.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260820.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>11.00%</t>
+          <t>10.84%</t>
         </is>
       </c>
     </row>
@@ -638,51 +638,51 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.54%</t>
+          <t>10.40%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>PWR US</t>
+          <t>VRT US</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>廣達服務公司</t>
+          <t>維諦技術控股公司</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>34,155</t>
+          <t>86,925</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.97%</t>
+          <t>7.99%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>VRT US</t>
+          <t>PWR US</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>維諦技術控股公司</t>
+          <t>廣達服務公司</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>86,925</t>
+          <t>34,155</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.81%</t>
+          <t>7.86%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.56%</t>
+          <t>5.54%</t>
         </is>
       </c>
     </row>
@@ -770,51 +770,51 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.35%</t>
+          <t>3.31%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>NVT US</t>
+          <t>HUBB US</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>nVent Electric PLC</t>
+          <t>安柏</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>56,759</t>
+          <t>18,679</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.07%</t>
+          <t>3.05%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>HUBB US</t>
+          <t>NVT US</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>安柏</t>
+          <t>nVent Electric PLC</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>18,679</t>
+          <t>56,759</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.06%</t>
+          <t>3.04%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.65%</t>
+          <t>2.64%</t>
         </is>
       </c>
     </row>
@@ -865,17 +865,17 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>EXC US</t>
+          <t>CEG US</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Exelon Corp</t>
+          <t>星座能源公司</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>131,101</t>
+          <t>21,631</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -887,22 +887,22 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>CEG US</t>
+          <t>EXC US</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>星座能源公司</t>
+          <t>Exelon Corp</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>21,631</t>
+          <t>131,101</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>2.05%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.79%</t>
+          <t>1.74%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.32%</t>
+          <t>1.33%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.28%</t>
         </is>
       </c>
     </row>
@@ -1019,17 +1019,17 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>FE US</t>
+          <t>ES US</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>第一能源公司</t>
+          <t>Eversource能源</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>74,101</t>
+          <t>48,160</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -1041,22 +1041,22 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>ES US</t>
+          <t>FE US</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Eversource能源</t>
+          <t>第一能源公司</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>48,160</t>
+          <t>74,101</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>1.21%</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.15%</t>
+          <t>1.16%</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>1.04%</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>1.03%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>1.02%</t>
         </is>
       </c>
     </row>
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>AEIS US</t>
+          <t>PPL US</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>艾儀有限公司</t>
+          <t>PPL公司</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>8,704</t>
+          <t>72,174</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>PPL US</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>PPL公司</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>72,174</t>
+          <t>140,345</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1283,39 +1283,39 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>AGX US</t>
+          <t>AEIS US</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>阿根公司</t>
+          <t>艾儀有限公司</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>4,721</t>
+          <t>8,704</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.88%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>ENS US</t>
+          <t>AGX US</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>EnerSys</t>
+          <t>阿根公司</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>12,752</t>
+          <t>4,721</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1327,22 +1327,22 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>ENS US</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>EnerSys</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>140,345</t>
+          <t>12,752</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.84%</t>
         </is>
       </c>
     </row>
@@ -1481,17 +1481,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>NRG US</t>
+          <t>PNW US</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>NRG Energy Inc</t>
+          <t>皮那可資本公司</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>12,924</t>
+          <t>15,527</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1503,22 +1503,22 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>PNW US</t>
+          <t>NRG US</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>皮那可資本公司</t>
+          <t>NRG Energy Inc</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>15,527</t>
+          <t>12,924</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.53%</t>
+          <t>0.52%</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.47%</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.41%</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.39%</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.31%</t>
+          <t>0.30%</t>
         </is>
       </c>
     </row>
@@ -1719,6 +1719,20 @@
           <t>0.01%</t>
         </is>
       </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>C_NTD</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr"/>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>155,977,309</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
